--- a/toy_models/farm_toy_v1_spine_storage.xlsx
+++ b/toy_models/farm_toy_v1_spine_storage.xlsx
@@ -123,12 +123,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -1291,33 +1291,202 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WHERE THE NUMBERS COME FROM</t>
+          <t>HAS THIS SHEET BEEN CHECKED?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Every crop constant and every planting calendar on the Model sheet is READ FROM THE APP by</t>
+          <t>Yes, and it is worth knowing how, because you should not have to take it on trust.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>toy_models/build_toy_v1.py - the same succession generator the solver uses, and the same</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>golden payload the tests pin. Nothing is retyped. See the 'Crop data' sheet for the values</t>
+          <t xml:space="preserve">  - Every crop constant and every planting date is READ FROM THE APP by the generator.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Nothing is retyped, so this sheet cannot quietly describe a different farm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The whole workbook is CALCULATED by a formula engine and compared, cell by cell, against</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    a separate model of the same arithmetic written from scratch. 52 weeks x 3 crops x 6 rows,</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    under two configurations - the shipped defaults AND a stressed one with shrink and sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    limits switched on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Every yellow input is changed and the sheet re-calculated, to prove it actually reaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the numbers at the bottom. An input wired to nothing is exactly the defect you found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Nothing on the Model sheet is a frozen number except the week strips and the week-1 zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Run it yourself:   .venv/bin/python toy_models/verify_toy_v1.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>YOU FOUND ONE OF THESE, AND IT IS WHY THE CHECKS ABOVE EXIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>'lb/harvest wk per acre' (column E) shipped as five typed numbers instead of formulas. The</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>harvest itself was always live - change sell-through and the real pounds did move - but that</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>one column sat frozen beside them, and would have disagreed the moment you touched a yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>A number printed next to a live one that can drift from it is this project's single most</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>repeated defect. Your inference was the right one: a stale value at the top is a reason to</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>check all of them. So all of them are now checked, every time the file is rebuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Also fixed in the same pass: 'Yield lb/acre' and 'm3 per lb' were live all along but were not</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>coloured yellow, so two of the biggest levers on the sheet looked like read-only reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>They are yellow now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>WHERE THE NUMBERS COME FROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Every crop constant and every planting calendar on the Model sheet is READ FROM THE APP by</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>toy_models/build_toy_v1.py - the same succession generator the solver uses, and the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>golden payload the tests pin. Nothing is retyped. See the 'Crop data' sheet for the values</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>and their sources. Re-run the generator after any crop-data change.</t>
         </is>
@@ -1437,7 +1606,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>lb/harvest wk at 1 acre</t>
+          <t>lb/harvest wk per acre</t>
         </is>
       </c>
     </row>
@@ -1460,8 +1629,9 @@
           <t>W16, W17</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>2125</v>
+      <c r="E6" s="9">
+        <f>$B$16*$C$16/2</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1483,8 +1653,9 @@
           <t>W40, W41</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>2125</v>
+      <c r="E7" s="9">
+        <f>$B$16*$C$16/2</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1506,8 +1677,9 @@
           <t>W21, W22, W23, W24</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>1700</v>
+      <c r="E8" s="9">
+        <f>$B$17*$C$17/4</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1529,8 +1701,9 @@
           <t>W41, W42, W43, W44</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>1700</v>
+      <c r="E9" s="9">
+        <f>$B$17*$C$17/4</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1552,8 +1725,9 @@
           <t>W30</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>8500</v>
+      <c r="E10" s="9">
+        <f>$B$18*$C$18/1</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1642,27 +1816,27 @@
           <t>Spinach</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>0.002197967741935484</v>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="11" t="n">
         <v>1000000</v>
       </c>
     </row>
@@ -1672,27 +1846,27 @@
           <t>Kale</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="11" t="n">
         <v>8000</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>0.003785388888888889</v>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="11" t="n">
         <v>1000000</v>
       </c>
     </row>
@@ -1702,13 +1876,13 @@
           <t>Garlic</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>0.001195385964912281</v>
       </c>
       <c r="E18" s="17" t="inlineStr">
@@ -1716,13 +1890,13 @@
           <t>Ambient</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="11" t="n">
         <v>1000000</v>
       </c>
     </row>
@@ -1746,7 +1920,7 @@
           <t>Cold store (cooler) capacity</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="11" t="n">
         <v>275</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1761,7 +1935,7 @@
           <t>Ambient store (barn) capacity</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
